--- a/pcb/pcb_model.xlsx
+++ b/pcb/pcb_model.xlsx
@@ -426,7 +426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>PCB 小链模型 v0.1（2026-10-20）。统一单位：百万颗 AI 加速器（KGI，不含 CPU）。满足率 = 供给 ÷ 需求（目标规格）。</t>
+          <t>PCB 小链模型 v0.2（2026-10-21）。满足率是预测口径（卖方供需表 + 本页分配），不是市场观测；可观测信号见页面"短缺检验"。统一单位：百万颗 AI 加速器（KGI，不含 CPU）。满足率 = 供给 ÷ 需求（目标规格）。</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HVLP3+ 高端铜箔</t>
+          <t>HVLP3+ 高端铜箔（预测缺口）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -654,17 +654,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>69%（预测）</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>72%（预测）</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>高盛 5 月：2025 年有效供给 803 ÷ 需求 679 吨/月；缺口 = （需求−有效供给）÷ 有效供给，2026/27 年 28%/39% [源11]。8 月上修到 45%–55% [源12]，本页取 2026 年 45%、2027 年 50%（满足率 = 1 ÷ 1.5 = 67%）（估）；再加大陆 HVLP4（德福 8 月 HVLP4 约 70 吨/月 [源17]、铜冠已量产 [源18]），假设 2027 年合计 +150 吨/月通过认证 （估），÷ 2027 年需求约 2,640 吨/月（2025→28 几何插值 （估））= +5.7 个百分点</t>
+          <t>&lt;b&gt;这是预测，不是市场观测&lt;/b&gt;：高盛 5 月：2025 年有效供给（扣良率 70–80%、换线损失后）803 ÷ 需求 679 吨/月，即 2025 年过剩；缺口 = （需求−有效供给）÷ 有效供给，2026/27 年 28%/39% [源11]。8 月把"2026–2028 年"缺口区间上修到 45%–55%（不分年）[源12]；&lt;b&gt;本页自行&lt;/b&gt;把它分配为 2026 年 45%、2027 年 50%（满足率 = 1 ÷ 1.5 = 67%）（估）。口径是 HVLP3+（2025 年需求里 HVLP3 占 76%），不是 HVLP4；市场信号只支持"HVLP4/5 认证瓶颈"（价格 ½、稼动率 ½）[源66,69]。反向口径：三井估 2030 年 HVLP3+ 需求约 2,400 吨/月 [源71]，比高盛插值的 2027 年还低；再加大陆 HVLP4（德福 8 月 HVLP4 约 70 吨/月 [源17]、铜冠已量产 [源18]），假设 2027 年合计 +150 吨/月通过认证 （估），÷ 2027 年需求约 2,640 吨/月（2025→28 几何插值 （估））= +5.7 个百分点</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1709,7 +1709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2537,6 +2537,381 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>56</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Prismark 2026-05《Global Leading PCB Companies – 2025》：全球 PCB 2024 年 736 亿 → 2025 年 858 亿美元（+16.7%）；领先的 AI 服务器 / 网络板厂增长超过 50%，多数板厂增长不到 10%</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://www.prismark.com/_files/ugd/950e51_7b4250411feb4f89a9c53d4a8aa5f3dd.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>57</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>MPBxChange 2026-09-24（引用 Prismark Q1 2026 产品分项：2026E 单双面 88、4–6 层 172、8–16 层 137、18 层以上 94、HDI 199、载板 192、柔性 137 亿美元，合计 1,020 亿；TPCA 2025 年 924 亿美元、泰国 50.6 亿美元；沪士汽车板毛利率约 −6.2pp；胜宏引用 AI 服务器 PCB 约 160 亿美元）</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://www.mpbxchange.com/research/world-pcb-market-2026-ai-servers-thailand</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>58</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>电子工程专辑 2026-06-27（Prismark 2025 年分产品：HDI +29.4%、多层板 +19.3%（18 层以上约 +80%）、载板 +18.2%、FPC +3.2%、普通板 +6.2%）</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://www.eet-china.com/mp/a505691.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>59</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>电子工程专辑 2026-04-23（Prismark：服务器 / 数据存储占 HDI 比重 2024 年 3.4% → 2025E 14.1% → 2030F 28.4%）</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://www.eet-china.com/mp/a489929.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>60</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>同花顺 2026-07-06（爱建证券，引用 Prismark）：2025 年服务器 / 数据存储 PCB 156.75 亿美元（+43.6%），有线通信 86.64 亿美元（+40.8%）；2025–30 年 CAAGR 载板 10.9%、HDI 9.2%、多层板 8.0%、柔性 3.8%；中国 2026 年至今公告 PCB 扩产约 712 亿元</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://stock.10jqka.com.cn/20260706/c677972164.shtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>61</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>界面新闻 2026-09-11：建滔年内第 7 次覆铜板涨价函；宏和电子布均价 4.81 → 11.91 元/米（+147.6%）；超声电子 PCB 毛利率 13.78%（−4.41pp）、崇达 7.67%（−4.62pp）、满坤净利 −30.5%；玻纤布产线 18–24 个月，2018 年后价格回落约两年；企业否认订单"锁到 2027/2028"，实际按月排单</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://www.jiemian.com/article/15081181.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>62</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>发现报告：PCB 需求分化专家纪要 2026-08-02（弱）：Q2 消费面积 −12–15%、价格 +35–40%；汽车面积 +7–8%；服务器 / 通信价格约 +10%；PP 缺口约 25%、CCL 约 15%；"高速 PCB 缺口远小于低速 PCB"</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://fxbaogao.com/detail/5576593</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>63</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>工商时报 2026-10-07：载板均价每季涨逾 7%，BT 续涨，紧张约两年，新厂 2029 年</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://www.ctee.com.tw/news/20261007700089-430502</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>64</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>MoneyDJ 2026-09-23（转述高盛）：ABF 缺口 8% → 34%；交期 3–4 个月 → 逾 12 个月；单季涨 10–15%；压膜设备交期 5–6 → 12–18 个月；存储厂试图回压 BT 价格 3–4%</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://www.moneydj.com/kmdj/news/newsviewer.aspx?a=b1ed20ff-51ed-41f6-ac0b-58ad03c696e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>65</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>钜亨网：欣兴 ABF 稼动率逾 90%、南电 ABF 约 85%、BT 满载</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6612993</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>66</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>工商时报 2026-10-10：金居 9 月营收 11.04 亿新台币（+64.63%）、Q3 31.69 亿（+59.78%）；法人称 2026 上半年以来陆续调涨高阶铜箔加工费约 5–10%</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://www.ctee.com.tw/news/20261010700086-439901</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>67</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>工商时报 2026-10-10：HVLP4 第四季月需求估破 1,000 吨；HVLP1/2 转 HVLP3/4 有效产能约减半</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://www.ctee.com.tw/news/20261010700084-439901</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>68</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>工商时报 2026-08-07：金居 2Q26 毛利率 27.39%（1Q26 28.71%），同比 +8.53pp</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://www.ctee.com.tw/news/20260807701501-430502</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>69</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>三井金属 FY2027/3 第 1 季说明会议事录：VSP 下半年销量预测由 840 下调到 730 吨/月，因马来西亚厂客户认证的手续性延迟；2025-10 与 2026-07 两次提价，并非所有等级统一调；VSP 提价全年增益 5–10 亿日元；竞争者进入低等级</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://www.mitsui-kinzoku.com/LinkClick.aspx?fileticket=Ch79AESSq6A%3D&amp;mid=1060&amp;tabid=159</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>70</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>三井金属 FY2027/3 第 1 季决算说明资料：VSP 月销量 FY25 平均 550 吨、FY26 Q1 660 吨、Q2 预计 720 吨；HVLP4 以上占比上半年约 45%、下半年约 60%</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://www2.jpx.co.jp/disc/57060/140120260804508317.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>71</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>三井金属 2026-01 机能材料事业说明会：2030 年 HVLP3+ 需求约 2,400 吨/月、HVLP4+ 约 1,400 吨/月；三井占 HVLP2+ 约 60%、HVLP5 约 80%</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://www.mitsui-kinzoku.com/LinkClick.aspx?fileticket=87CifTthi%2F0%3D&amp;mid=1060&amp;tabid=100</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>72</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>发现报告：国金证券点评三井金属 Q1：铜箔"价格平稳"</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://fxbaogao.com/detail/5417878</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>73</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>德福科技 投资者关系活动记录表 2026-09-09（巨潮）：8 月 HVLP 约 500 吨、HVLP4 约 70 吨；HVLP1–3 良率近 70%、HVLP4 约 60%；"低端铜箔竞争激烈，高端铜箔有效供给相对紧张"</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://static.cninfo.com.cn/finalpage/2026-09-09/1225555887.PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>74</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>铜冠铜箔 2026 半年报（巨潮）：PCB 铜箔营收 25.07 亿元（+47.16%）、毛利率 11.60%（+6.04pp）；稼动率 90.6%；出货以 HVLP2 为主</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>http://static.cninfo.com.cn/finalpage/2026-08-27/1225509625.PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>75</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>古河电工 2026-08-06 说明会问答：铜箔全年展望因高功能箔比重上升上调约 25 亿日元</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://www.furukawaelectric.com/ir/library/finalreport/pdf/2027/20260806_online-qa.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>76</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>东方财富财富号 2026-06-17（自媒体转述券商，弱）：日系 HVLP 对大陆客户交期 6–8 个月、预付款、2–3 年长约；表面处理机交期 18–24 个月</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>https://caifuhao.eastmoney.com/news/20260617002336111466320</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>77</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>钜亨号·北风窗 2026-10-16（专家纪要，弱）：HVLP4 加工费 22–25 万元/吨；2026 年铜箔调价三次各约 10%；"玻璃布缺口最大，铜箔排第二"；部分 PCB 厂开始压低端 RTF/HTE 价格</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://hao.cnyes.com/post/272720</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>78</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>珠海报业 2026-01-12：富山工业园排污总量指标接近饱和（环评约束个案）</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://pub-static.hizh.cn/a/202601/12/AP6964c221e4b086489718fbb6.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>79</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>本站铜页 v0.1：LME 铜季度均价 2025Q3 9,792 → 2026Q3 14,120 美元/吨（+44%）</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>cu.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>80</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>本站 PCB 页 v1 存档（2026-10-20 版）：改判前的原文，供对照</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>pcb_v1.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pcb/pcb_model.xlsx
+++ b/pcb/pcb_model.xlsx
@@ -1709,7 +1709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C80"/>
+  <dimension ref="A1:C94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2912,6 +2912,216 @@
         </is>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>81</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Prismark 2026-05《Global Leading PCB Companies – 2025》排名表：2025 年臻鼎 58.69 亿美元、欣兴 42.25、东山 35.70、深南 32.95、TTM 29.06、沪电 27.60、胜宏 26.86、华通 24.46、健鼎 23.61、旗胜 22.73；前 100 大合计 871.5 亿美元（含组装与非 PCB 收入约 13.6%）；中国大陆企业约占 36% 产值、台湾约 30%；前 40 大净利率 8.3%</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://www.prismark.com/_files/ugd/950e51_7b4250411feb4f89a9c53d4a8aa5f3dd.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>82</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>工商时报 2026-08-03（IEK 转载）：Prismark 2025 年 CCL（扣除大宗标准型、含 PP）市场 186.76 亿美元（+24.4%）；台光电 16.2%、生益 13.2%、建滔 12.4%；台系四家（台光电、南亚、联茂、台燿）合计 34.4%</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://ieknet.iek.org.tw/ieknews/news_open.aspx?nsl_id=993f82be5979424284e465e5ae7ea779</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>83</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>中央社 2025-04-28（引 TPCA）：全球载板前 5 大 欣兴 16%、SEMCO 9.9%、Ibiden 9.3%、AT&amp;S 9.1%、南电 8.7%，合计过半；台湾占载板产值 32.8%、日本 27.6%、韩国 27%</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://www.cna.com.tw/news/afe/202504280185.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>84</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>味之素官网故事页（2026）：ABF 1999 年上市，FC-BGA 绝缘积层膜全球份额“约 95%”（公司自述）</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://www.ajinomoto.com/zh-CN/stories/the-ajinomoto-groups-unexpected-role-in-semiconductor-manufacturing-the-insulating-film-abf-born-from-aminoscience</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>85</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Electronics Weekly 2025-07（Yole《Status of the Advanced IC Substrate Industry 2025》）：先进 IC 载板 2024 年 142 亿美元，2030 年 310 亿美元</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://www.electronicsweekly.com/news/business/substrate-market-to-be-worth-31bn-by-2030-2025-07/</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>86</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>大族数控 2025 年年报摘要（巨潮 2026-03-31）：机械钻孔机“根据 Prismark 市场预测及公司交付数据测算”2025 年全球份额约 50%；灼识咨询：2024 年 PCB 专用设备全球份额 6.5%（第一）</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://static.cninfo.com.cn/finalpage/2026-03-31/1225057159.PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>87</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Panasonic MEGTRON6 产品页：R-5775(N) Dk 3.34 / Df 0.0037 @13GHz（典型值）</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://industrial.panasonic.com/ww/products/pt/megtron/megtron6</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>88</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Panasonic MEGTRON7 产品页：R-5785(N) Dk 3.31 / Df 0.0023 @14GHz（典型值）</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>https://industrial.panasonic.com/ww/products/pt/megtron/megtron7</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>89</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Panasonic MEGTRON8 数据表：R-5795(U) Dk 3.08 / Df 0.0012 @14GHz（典型值）</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>https://industrial.panasonic.com/content/data/EM/PDF/ipcdatasheet_R-5795.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>90</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>三井金属（台湾三井铜箔）HSD 铜箔路线图：B 面粗糙度 Rz HVLP 1.5 / HVLP2 1.0 / HVLP3 0.6 / HVLP4 0.5 / HVLP5 0.4 μm（代表值，HVLP5 送样中）</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>https://www.tcf.com.tw/download/50/</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>91</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Electronic Design 2017-10-24：mSAP 用于 HDI，线宽/线距 30/30 μm 走向 25/25、20/20；薄铜 + 图形电镀，线形接近矩形</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>https://www.electronicdesign.com/markets/automation/article/21805746/msap-the-new-pcb-manufacturing-imperative-for-5g-smartphones</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>92</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>TrendForce 2025-07-30：CoWoP（芯片 + 中介层直接贴 PCB，省掉 ABF 载板）仍很早期；板厂存疑；要替代 ABF，PCB 线宽线距需从 20/35 μm 缩到 10/10 μm 以下</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>https://www.trendforce.com/news/2025/07/30/news-cowop-a-game-changer-beyond-cowos-or-just-hype-pcb-makers-stay-skeptical/</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>93</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Tushare Pro 财务接口（现金流量表、资产负债表、利润表、财务指标，数据源自上市公司定期报告），17 家 A 股 PCB 链公司 FY2015–2025 + 2026H1，2026-10-23 拉取。资本开支 = 购建固定资产、无形资产和其他长期资产支付的现金；折旧 = 现金流量表补充资料的固定资产折旧；在建工程取资产负债表；ROIC、毛利率为 Tushare 口径。2026H1 为半年数，未年化。整理结果：pcb_data/filings.json</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>pcb_data/filings.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>94</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>巨潮资讯网：12 家公司 2021–2025 年年度报告“主要销售客户情况”（前五名客户合计销售额占年度销售总额比例），2026-10-23 下载核对；逐份年报链接见 pcb_data/top5.json</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>pcb_data/top5.json</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pcb/pcb_model.xlsx
+++ b/pcb/pcb_model.xlsx
@@ -1709,7 +1709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C94"/>
+  <dimension ref="A1:C97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3122,6 +3122,51 @@
         </is>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>95</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Tushare Pro 分红送股（dividend，取“实施”记录，现金分红 = 每股派息（税前）× 基准股本，按除息日所在年份归年）与股票回购（repurchase，取“完成”记录；同一回购方案的“完成”行是累计进度，按方案取最大值；剔除价格上下限相同且金额 &lt; 0.2 亿元的限制性股票回购注销），18 家（17 家 + 兴森科技），2026-10-24 拉取；兴森科技财报口径同 tsfin。整理结果：pcb_data/scorecard.json</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>pcb_data/scorecard.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>96</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>MOPS 季报（经 FinMind API 下载）：欣兴 3037、南电 8046、景硕 3189 季度营收与毛利率，2019Q1–2026Q2，2026-10-24 下载；整理结果：pcb_data/scorecard.json</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>https://api.finmindtrade.com/api/v4/data?dataset=TaiwanStockFinancialStatements&amp;data_id=8046&amp;start_date=2019-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>97</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>巨潮资讯网：宏和科技、鼎泰高科、兴森科技 2021–2025 年年度报告“主要销售客户情况”（前五名客户合计销售额占年度销售总额比例；鼎泰 2022 年上市，无 2021 年报），2026-10-24 下载核对；逐份年报链接见 pcb_data/scorecard.json</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>pcb_data/scorecard.json</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
